--- a/output/topology_excel/7620.xlsx
+++ b/output/topology_excel/7620.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,7 +465,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,18 +740,18 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>277</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
         <v>13</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>118</v>
+        <v>373</v>
       </c>
       <c r="F16" t="n">
         <v>13</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>166</v>
+        <v>277</v>
       </c>
       <c r="F18" t="n">
         <v>13</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>245</v>
       </c>
       <c r="F20" t="n">
         <v>13</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>297</v>
+        <v>118</v>
       </c>
       <c r="F22" t="n">
-        <v>76</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -927,7 +927,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>373</v>
+        <v>111</v>
       </c>
       <c r="F23" t="n">
         <v>13</v>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>432</v>
+        <v>166</v>
       </c>
       <c r="F24" t="n">
         <v>13</v>
@@ -968,10 +968,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,15 +1004,15 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>139</v>
+        <v>432</v>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27" t="n">
         <v>9</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="F28" t="n">
         <v>12</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="F29" t="n">
         <v>12</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,18 +1092,18 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>166</v>
+        <v>297</v>
       </c>
       <c r="F30" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F31" t="n">
         <v>12</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="F32" t="n">
-        <v>211</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="F33" t="n">
         <v>12</v>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="F34" t="n">
-        <v>12</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B35" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1206,6 +1206,138 @@
       </c>
       <c r="F35" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>139</v>
+      </c>
+      <c r="F36" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>11</v>
+      </c>
+      <c r="B37" t="n">
+        <v>14</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>338</v>
+      </c>
+      <c r="F37" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>15</v>
+      </c>
+      <c r="B38" t="n">
+        <v>16</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>46</v>
+      </c>
+      <c r="F38" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" t="n">
+        <v>13</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>169</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>99</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="n">
+        <v>13</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>180</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/7620.xlsx
+++ b/output/topology_excel/7620.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>179</v>
@@ -743,7 +743,7 @@
         <v>339</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1095,7 +1095,7 @@
         <v>297</v>
       </c>
       <c r="F30" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -1183,7 +1183,7 @@
         <v>224</v>
       </c>
       <c r="F34" t="n">
-        <v>211</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
